--- a/Rentable_Items_vs_Lease_Audit_Reconciliation.xlsx
+++ b/Rentable_Items_vs_Lease_Audit_Reconciliation.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Garage Reconciliation" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Storage Reconciliation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Rent Roll Cross-Check" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Garage Reconciliation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Storage Reconciliation" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -103,9 +104,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -501,9 +500,9 @@
   <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" style="3" min="1" max="1"/>
+    <col width="34" customWidth="1" style="3" min="2" max="2"/>
+    <col width="8" customWidth="1" style="3" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -535,7 +534,6 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
@@ -546,7 +544,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>DOC GAP</t>
@@ -557,7 +554,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>CONTRADICTION</t>
@@ -568,7 +564,6 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>NOT IN AUDIT</t>
@@ -579,7 +574,6 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>NO AUDIT NOTE</t>
@@ -590,7 +584,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>Out of Service</t>
@@ -601,7 +594,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>ID CONFLICT</t>
@@ -619,7 +611,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>DOC GAP</t>
@@ -630,7 +621,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
@@ -641,7 +631,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>CONTRADICTION</t>
@@ -652,7 +641,6 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
           <t>REVIEW (audit notes W&amp;D not storage)</t>
@@ -670,65 +658,60 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
           <t>CONFIRMED</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Lease audit corroborates the charge / addendum on file</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
           <t>DOC GAP</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Charged on rent roll but no supporting lease addendum found in file</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
           <t>CONTRADICTION</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Lease audit says NO charge / $0 on rent roll / no garage-storage at all</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
           <t>ID CONFLICT</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Item ID assigned to a different unit between report and lease addendum</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
           <t>NOT IN AUDIT</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Unit not present in the 06/01 lease audit</t>
         </is>
@@ -745,1376 +728,285 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" style="3" min="1" max="1"/>
+    <col width="18" customWidth="1" style="3" min="2" max="2"/>
+    <col width="20" customWidth="1" style="3" min="3" max="3"/>
+    <col width="14" customWidth="1" style="3" min="4" max="4"/>
+    <col width="12" customWidth="1" style="3" min="5" max="5"/>
+    <col width="13" customWidth="1" style="3" min="6" max="6"/>
+    <col width="70" customWidth="1" style="3" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Garage</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>RENTABLE ITEMS REPORT  vs  RENT ROLL DETAIL (Sheet1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Report as of 06/19/2026   |   Rent Roll as of 06/01/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>RESULT: The report matches the rent roll's billed charges almost exactly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Garage charge total:  Report $5,175  =  Rent Roll $5,175   (exact match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Storage charge total:  Report $1,880  =  Rent Roll $1,880   (exact match)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Per unit: 31 of 32 garage units and 45 of 46 storage units match to the dollar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • The 3 exceptions below net to $0 in total</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>THE 3 LINE-ITEM EXCEPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Tenant (report)</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Sched Amt</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Flag</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Lease Audit note / reason</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>1-A</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>04-110</t>
-        </is>
-      </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>Wood, Justin</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-      <c r="G2" s="5" t="inlineStr">
-        <is>
-          <t>No garage/parking addendum in lease packet</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>1-B</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>01-102</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>McNeely, Jason</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>NTV</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr">
-        <is>
-          <t>$175</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>No garage on lease, but there's a garage charge on rent roll</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>1-C</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>01-110</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Gomez, Sarah</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>Garage space 1-C per Enclosed Garage Addendum - $300/month on rent roll</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>1-D</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>01-110</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Gomez, Sarah</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Garage space 1-C per Enclosed Garage Addendum - $300/month on rent roll</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>1-E</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>01-204</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Wiles, Brian</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F6" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Garage space 1-E per Enclosed Garage Addendum - $150/month per rent roll and addendum</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>1-F</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>02-102</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Williams, Robert</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>NTV</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Garage space 1-F per Enclosed Garage Addendum. $150/month per rent roll</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>2-A</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>10-204</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Johnson, Derek</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr">
-        <is>
-          <t>Garage rent roll = $150/month; garage/parking addendum could not be verified (lease not found in Drive)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>2-B</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>02-208</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Mcgloin, Stephen</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>ID CONFLICT</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Lease addendum assigns garage 2-B to unit 10-303 (Smalls); report bills it to 02-208 (Mcgloin)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>2-C</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>10-209</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Smith, Shanta</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
-        <is>
-          <t>Parking Addendum in packet; parking cost blank per addendum ($150/month per rent roll)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>2-D</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>02-208</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Mcgloin, Stephen</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>CONTRADICTION</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>No garage addendum found; no garage charge on rent roll</t>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Tenant</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Rent Roll</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Explanation</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>2-E</t>
+          <t>07-102</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>07-102</t>
+          <t>Williams, Tyra</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>Williams, Tyra</t>
+          <t>Garage 2-E</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>In Use</t>
+          <t>$150</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="inlineStr">
-        <is>
-          <t>CONTRADICTION</t>
+          <t>$0</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>Timing</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>No garage</t>
+          <t>Garage assigned 06/04/2026 — AFTER the 06/01 rent roll. Not an error; verify the $150 now appears on the current rent roll.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>2-F</t>
+          <t>10-309</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>04-210</t>
+          <t>Iaea Iese, Hope</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Chapman, Christopher</t>
+          <t>Storage S10-5 + S10-7</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>In Use</t>
+          <t>$80 (2 units)</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
+          <t>$40 (1 unit)</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Timing</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>No garage addendum in renewal packet</t>
+          <t>2nd storage (S10-7) assigned 06/09/2026 — AFTER the 06/01 rent roll. Verify the 2nd $40 is now billed (current storage is fully conceded to $0).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>3-A</t>
+          <t>10-304</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>09-206</t>
+          <t>Tucker, Hunter</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Peterson, Vernon</t>
+          <t>Storage S2-8</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>In Use</t>
+          <t>$0 (unassigned)</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
+          <t>$40</t>
+        </is>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>GENUINE GAP</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Enclosed garage addendum in packet; $150/month per rent roll</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>3-B</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>02-210</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Konegan, Joseph</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr">
-        <is>
-          <t>$150 GARAGE on rent roll but no Enclosed Garage Addendum found in DR Horton Move-in lease package</t>
+          <t>Resident is billed $40 storage AND the lease has a storage addendum (S2-8), but the report shows S2-8 UNASSIGNED. The physical unit is not linked in OneSite's rentable-items module. Assign S2-8 to 10-304.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>3-C</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>05-109</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>LeBlanc, Christopher</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr">
-        <is>
-          <t>No garage addendum</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>NOTE ON THE LEASE-AUDIT 'CONTRADICTION' FLAGS</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>3-D</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>10-310</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Taylor, Carlee</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>No enclosed garage addendum found in move-in lease packet ($150/month garage per rent roll)</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>The earlier comparison flagged many garages/storage where the Lease Audit's free-text note said</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>3-E</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>04-104</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Davis, Jamie</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>$175</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>Garage space 3-E per Enclosed Garage Addendum (no monthly fee listed in addendum)</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>'No garage' or 'no charge on rent roll.' Cross-checking the actual Rent Roll Detail shows those</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>3-F</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>03-303</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Hering, Natascha</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F19" s="10" t="inlineStr">
-        <is>
-          <t>NO AUDIT NOTE</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>charges DO exist and the report matches them. So those are NOT report errors — the Lease Audit's</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>4-A</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>06-310</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Monk, Isaac</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>NTV</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F20" s="11" t="inlineStr">
-        <is>
-          <t>NOT IN AUDIT</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>Unit not present in lease audit (audit is as-of 06/01; report as-of 06/19)</t>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>narrative notes were the unreliable part (they describe lease-document gaps, not the billed rent roll).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>4-B</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>05-304</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Roebuck, Jordan</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>No garage addendum</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>4-C</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>06-103</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Alvarez Rivera, Jose</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>No garage addendum</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Also: garage space 2-B (lease says unit 10-303) and storage S4-3 (lease says 04-106) — the rent roll</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>4-D</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>08-104</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Heidrich, John</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G23" s="5" t="inlineStr">
-        <is>
-          <t>Enclosed garage: $300/month per lease (ENCLOSED GARAGE ADDENDUM in packet)</t>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>bills the units the REPORT shows (02-208 and 04-105), so the report matches billing; only the lease</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>4-E</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>06-306</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Champagne, Carl</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>NTV</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>CONTRADICTION</t>
-        </is>
-      </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>Enclosed Garage Addendum (4-E) signed; $0 on rent roll garage column</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>paperwork's space label differs. And rent roll unit 09-208 has 'A315' typed in the GARAGE dollar</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>4-F</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>08-104</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Heidrich, John</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>Enclosed garage: $300/month per lease (ENCLOSED GARAGE ADDENDUM in packet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>5-A</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>05-202</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Farnham, Michael</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Leased</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr">
-        <is>
-          <t>NOT IN AUDIT</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>Unit not present in lease audit (audit is as-of 06/01; report as-of 06/19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>5-B</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>07-104</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Meide, Jacob</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>CONTRADICTION</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>No garage</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>5-C</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>05-306</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Freeman, Kayla</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G28" s="5" t="inlineStr">
-        <is>
-          <t>Storage unit 5-C per enclosed garage addendum; $150/mo per rent roll</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>5-D</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>06-105</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Brooks, Sandra</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>CONTRADICTION</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
-        <is>
-          <t>No garage</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="inlineStr">
-        <is>
-          <t>5-E</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>07-101</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Bryant, James</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>$175</t>
-        </is>
-      </c>
-      <c r="F30" s="9" t="inlineStr">
-        <is>
-          <t>CONTRADICTION</t>
-        </is>
-      </c>
-      <c r="G30" s="5" t="inlineStr">
-        <is>
-          <t>No garage</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>5-F</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>07-205</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Huggins, Alyssa</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>CONTRADICTION</t>
-        </is>
-      </c>
-      <c r="G31" s="5" t="inlineStr">
-        <is>
-          <t>No garage</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>6-A</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>07-304</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>Hubner, Nicholas</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>CONTRADICTION</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="inlineStr">
-        <is>
-          <t>No garage</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>6-B</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>08-105</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Ramdorsingh, Cindy</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F33" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G33" s="5" t="inlineStr">
-        <is>
-          <t>Enclosed garage: $150/month per lease (ENCLOSED GARAGE ADDENDUM in packet)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>6-C</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="inlineStr">
-        <is>
-          <t>08-309</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Cooper, Ramon</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>DOC GAP</t>
-        </is>
-      </c>
-      <c r="G34" s="5" t="inlineStr">
-        <is>
-          <t>Renewal lease packet not found in Drive</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="inlineStr">
-        <is>
-          <t>6-D</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>08-306</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>Sible, Steven</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G35" s="5" t="inlineStr">
-        <is>
-          <t>Enclosed garage addendum in packet; $150/month (space 6-D) per addendum = $150 on rent roll</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>6-E</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>(Out of Service / Unassigned)</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="inlineStr">
-        <is>
-          <t>Out of Service</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="G36" s="5" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>6-F</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>08-205</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Basham, Dylan</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>In Use</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>CONFIRMED</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>Enclosed garage: $150/month per lease (ENCLOSED GARAGE ADDENDUM in packet)</t>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>column (a surface-parking label, not an enclosed garage) — a data-entry cleanup item, not in scope.</t>
         </is>
       </c>
     </row>
@@ -2129,20 +1021,1404 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" style="3" min="1" max="1"/>
+    <col width="10" customWidth="1" style="3" min="2" max="2"/>
+    <col width="24" customWidth="1" style="3" min="3" max="3"/>
+    <col width="12" customWidth="1" style="3" min="4" max="4"/>
+    <col width="10" customWidth="1" style="3" min="5" max="5"/>
+    <col width="22" customWidth="1" style="3" min="6" max="6"/>
+    <col width="60" customWidth="1" style="3" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
+          <t>Garage</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Tenant (report)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Sched Amt</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Flag</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Lease Audit note / reason</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>1-A</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>04-110</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Wood, Justin</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>No garage/parking addendum in lease packet</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>1-B</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>01-102</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>McNeely, Jason</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>NTV</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>$175</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>No garage on lease, but there's a garage charge on rent roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>1-C</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>01-110</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Gomez, Sarah</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>Garage space 1-C per Enclosed Garage Addendum - $300/month on rent roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>1-D</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>01-110</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Gomez, Sarah</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>Garage space 1-C per Enclosed Garage Addendum - $300/month on rent roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>1-E</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>01-204</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Wiles, Brian</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Garage space 1-E per Enclosed Garage Addendum - $150/month per rent roll and addendum</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>1-F</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>02-102</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Williams, Robert</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>NTV</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>Garage space 1-F per Enclosed Garage Addendum. $150/month per rent roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2-A</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>10-204</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Johnson, Derek</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Garage rent roll = $150/month; garage/parking addendum could not be verified (lease not found in Drive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2-B</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>02-208</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Mcgloin, Stephen</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>ID CONFLICT</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>Lease addendum assigns garage 2-B to unit 10-303 (Smalls); report bills it to 02-208 (Mcgloin)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>2-C</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>10-209</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Smith, Shanta</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Parking Addendum in packet; parking cost blank per addendum ($150/month per rent roll)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2-D</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>02-208</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Mcgloin, Stephen</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>CONTRADICTION</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>No garage addendum found; no garage charge on rent roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>2-E</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>07-102</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Williams, Tyra</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>CONTRADICTION</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>No garage</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2-F</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>04-210</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Chapman, Christopher</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>No garage addendum in renewal packet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>3-A</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>09-206</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Peterson, Vernon</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>Enclosed garage addendum in packet; $150/month per rent roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>3-B</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>02-210</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Konegan, Joseph</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>$150 GARAGE on rent roll but no Enclosed Garage Addendum found in DR Horton Move-in lease package</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>3-C</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>05-109</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>LeBlanc, Christopher</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>No garage addendum</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>3-D</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>10-310</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Taylor, Carlee</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>No enclosed garage addendum found in move-in lease packet ($150/month garage per rent roll)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>3-E</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>04-104</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Davis, Jamie</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>$175</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Garage space 3-E per Enclosed Garage Addendum (no monthly fee listed in addendum)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>3-F</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>03-303</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Hering, Natascha</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
+        <is>
+          <t>NO AUDIT NOTE</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>4-A</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>06-310</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Monk, Isaac</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>NTV</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr">
+        <is>
+          <t>NOT IN AUDIT</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Unit not present in lease audit (audit is as-of 06/01; report as-of 06/19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>4-B</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>05-304</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Roebuck, Jordan</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>No garage addendum</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>4-C</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>06-103</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Alvarez Rivera, Jose</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>No garage addendum</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>4-D</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>08-104</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Heidrich, John</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Enclosed garage: $300/month per lease (ENCLOSED GARAGE ADDENDUM in packet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>4-E</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>06-306</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Champagne, Carl</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>NTV</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>CONTRADICTION</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Enclosed Garage Addendum (4-E) signed; $0 on rent roll garage column</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>4-F</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>08-104</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Heidrich, John</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Enclosed garage: $300/month per lease (ENCLOSED GARAGE ADDENDUM in packet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>5-A</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>05-202</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Farnham, Michael</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Leased</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>NOT IN AUDIT</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Unit not present in lease audit (audit is as-of 06/01; report as-of 06/19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>5-B</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>07-104</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Meide, Jacob</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>CONTRADICTION</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>No garage</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>5-C</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>05-306</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Freeman, Kayla</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Storage unit 5-C per enclosed garage addendum; $150/mo per rent roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>5-D</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>06-105</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Brooks, Sandra</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>CONTRADICTION</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>No garage</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>5-E</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>07-101</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Bryant, James</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>$175</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>CONTRADICTION</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>No garage</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>5-F</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>07-205</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Huggins, Alyssa</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>CONTRADICTION</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>No garage</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>6-A</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>07-304</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Hubner, Nicholas</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>CONTRADICTION</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>No garage</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>6-B</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>08-105</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Ramdorsingh, Cindy</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Enclosed garage: $150/month per lease (ENCLOSED GARAGE ADDENDUM in packet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>6-C</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>08-309</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Cooper, Ramon</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>DOC GAP</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Renewal lease packet not found in Drive</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>6-D</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>08-306</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Sible, Steven</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Enclosed garage addendum in packet; $150/month (space 6-D) per addendum = $150 on rent roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>6-E</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>(Out of Service / Unassigned)</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Out of Service</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>6-F</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>08-205</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Basham, Dylan</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>In Use</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>CONFIRMED</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Enclosed garage: $150/month per lease (ENCLOSED GARAGE ADDENDUM in packet)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="3" min="1" max="1"/>
+    <col width="10" customWidth="1" style="3" min="2" max="2"/>
+    <col width="24" customWidth="1" style="3" min="3" max="3"/>
+    <col width="12" customWidth="1" style="3" min="4" max="4"/>
+    <col width="10" customWidth="1" style="3" min="5" max="5"/>
+    <col width="22" customWidth="1" style="3" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
           <t>Storage</t>
         </is>
       </c>
